--- a/SQExcel.Portal/src/content/docs/ja/docs/images/medium-scale/medium-scale.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/medium-scale/medium-scale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\medium-scale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\medium-scale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAE005C-E8A1-421C-A8C2-BE192ED57A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49729B10-8CD5-4949-AC5A-58D2CDDA9327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1490" yWindow="30" windowWidth="21890" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="16680" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MEDIUM_SCALE" sheetId="5" r:id="rId1"/>
@@ -2298,508 +2298,6 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>72339</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F476092-5A66-293C-C917-B3765571034D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="469900" y="1143000"/>
-          <a:ext cx="10801350" cy="7844739"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>224117</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>201708</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>221129</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>78806</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="24" name="グループ化 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE418A9D-CDFD-601C-149F-DBF4B8C80635}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="455705" y="10854767"/>
-          <a:ext cx="10650071" cy="6593157"/>
-          <a:chOff x="459067" y="10717308"/>
-          <a:chExt cx="10804712" cy="6506498"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="23" name="図 22">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED353DAB-A919-4F2C-8C52-F7409EE1E779}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="459067" y="10717308"/>
-            <a:ext cx="10804712" cy="6506498"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="正方形/長方形 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47E50CF8-B305-43FB-A6C6-101537862BFB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5193966" y="11201771"/>
-            <a:ext cx="3443925" cy="331650"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="正方形/長方形 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58089218-FD46-281A-D19C-7E7C6F409CB3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3520554" y="12136120"/>
-            <a:ext cx="5139425" cy="608713"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="8" name="正方形/長方形 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36D47D2D-C69E-E03F-2546-3AAA43961B5A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8777110" y="11815068"/>
-            <a:ext cx="2305309" cy="396753"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>7472</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>116159</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="44" name="グループ化 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA74142D-2B48-E12C-8C57-0768AE39B595}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="18534531"/>
-          <a:ext cx="10650071" cy="6593157"/>
-          <a:chOff x="469900" y="18310414"/>
-          <a:chExt cx="10801350" cy="6509487"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="38" name="図 37">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C27DE72-12A1-671D-F9A9-A5A99D9431EF}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="18310414"/>
-            <a:ext cx="10801350" cy="6509487"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="正方形/長方形 9">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C7D4346-2743-47D1-97EE-E86C211126A3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5217465" y="18782646"/>
-            <a:ext cx="3442756" cy="335950"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="11" name="正方形/長方形 10">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78B252B8-1B3C-4915-8925-69E22E8AB1BA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3547271" y="19720078"/>
-            <a:ext cx="5134729" cy="813751"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="正方形/長方形 11">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACD207F6-E661-4551-AE4E-735EDCA28E53}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8800851" y="19400875"/>
-            <a:ext cx="2306640" cy="722803"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>151</xdr:row>
       <xdr:rowOff>136072</xdr:rowOff>
     </xdr:from>
@@ -2823,7 +2321,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2867,7 +2365,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2910,8 +2408,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="481319" y="43325144"/>
-          <a:ext cx="10645802" cy="6420016"/>
+          <a:off x="484308" y="43604544"/>
+          <a:ext cx="10714531" cy="6460358"/>
           <a:chOff x="271236" y="42336358"/>
           <a:chExt cx="10800443" cy="6339334"/>
         </a:xfrm>
@@ -2930,7 +2428,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3005,23 +2503,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>9071</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>17930</xdr:colOff>
       <xdr:row>220</xdr:row>
-      <xdr:rowOff>208643</xdr:rowOff>
+      <xdr:rowOff>125505</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>1814</xdr:colOff>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>189380</xdr:colOff>
       <xdr:row>240</xdr:row>
-      <xdr:rowOff>145440</xdr:rowOff>
+      <xdr:rowOff>197469</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="21" name="グループ化 20">
+        <xdr:cNvPr id="54" name="グループ化 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBDD9A7A-33D2-94BA-6181-ECC7D4FD69E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97BC2643-1563-25FF-6D8B-BF6D32EFCBB5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3029,18 +2527,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="472247" y="51158055"/>
-          <a:ext cx="10645802" cy="4568561"/>
-          <a:chOff x="253092" y="50301072"/>
-          <a:chExt cx="10800443" cy="4506982"/>
+          <a:off x="251012" y="51403623"/>
+          <a:ext cx="10660156" cy="4733611"/>
+          <a:chOff x="254150" y="50417505"/>
+          <a:chExt cx="10801350" cy="4643964"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="19" name="図 18">
+          <xdr:cNvPr id="48" name="図 47">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AC5B951-1FF9-503D-7031-ABAFE6534796}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{878276D0-1736-11DD-7C92-0615C3C0D1B4}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3049,15 +2547,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="253092" y="50301072"/>
-            <a:ext cx="10800443" cy="4506982"/>
+            <a:off x="254150" y="50417505"/>
+            <a:ext cx="10801350" cy="4643964"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3077,8 +2575,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1374321" y="52714072"/>
-            <a:ext cx="9451521" cy="703943"/>
+            <a:off x="1761117" y="52913304"/>
+            <a:ext cx="7421432" cy="722530"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3125,22 +2623,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>272</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>313</xdr:row>
+      <xdr:rowOff>8965</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>307</xdr:row>
-      <xdr:rowOff>188258</xdr:rowOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>171451</xdr:colOff>
+      <xdr:row>335</xdr:row>
+      <xdr:rowOff>91356</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="30" name="グループ化 29">
+        <xdr:cNvPr id="58" name="グループ化 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4852424-7306-A2E5-AA62-C59425A66CBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{044352B9-EA36-7F45-E640-7BC6316E98DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3148,18 +2646,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="463176" y="62992001"/>
-          <a:ext cx="8520057" cy="8293845"/>
-          <a:chOff x="469900" y="61722001"/>
-          <a:chExt cx="8641080" cy="8189257"/>
+          <a:off x="466166" y="72963741"/>
+          <a:ext cx="10660156" cy="5210203"/>
+          <a:chOff x="490370" y="71596624"/>
+          <a:chExt cx="10801350" cy="5111591"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="26" name="図 25">
+          <xdr:cNvPr id="57" name="図 56">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05AD6181-0912-2CE4-3FFA-EB8CA8896AEE}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2BC5D9E-A308-258F-9157-069310B674DF}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3168,189 +2666,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="469900" y="61722001"/>
-            <a:ext cx="8641080" cy="8189257"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="28" name="正方形/長方形 27">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{094D0CCA-FA1E-42B3-9802-5B8F43E9A4D0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="596901" y="65660494"/>
-            <a:ext cx="872564" cy="318247"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="29" name="正方形/長方形 28">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BBBC4DF-764A-DA27-9ABB-9C4862B96257}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="604371" y="62872470"/>
-            <a:ext cx="6056405" cy="318247"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>313</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>336</xdr:row>
-      <xdr:rowOff>145144</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="33" name="グループ化 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E355C64-18EF-9E74-DC29-66DA1E991009}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="72487118"/>
-          <a:ext cx="10650071" cy="5471673"/>
-          <a:chOff x="469900" y="71551800"/>
-          <a:chExt cx="10801350" cy="5402944"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="27" name="図 26">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F43212A-3233-E78E-038D-635EE977EF26}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="469900" y="71551800"/>
-            <a:ext cx="10801350" cy="4664371"/>
+            <a:off x="490370" y="71596624"/>
+            <a:ext cx="10801350" cy="4487720"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3370,8 +2694,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="679077" y="72859153"/>
-            <a:ext cx="3792444" cy="236069"/>
+            <a:off x="679989" y="72861687"/>
+            <a:ext cx="3816275" cy="236090"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3425,8 +2749,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1174750" y="76352401"/>
-            <a:ext cx="2097314" cy="602343"/>
+            <a:off x="1217077" y="76107826"/>
+            <a:ext cx="2109234" cy="600389"/>
           </a:xfrm>
           <a:prstGeom prst="wedgeRectCallout">
             <a:avLst>
@@ -3499,180 +2823,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>119533</xdr:colOff>
-      <xdr:row>342</xdr:row>
-      <xdr:rowOff>231588</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>116545</xdr:colOff>
-      <xdr:row>371</xdr:row>
-      <xdr:rowOff>108686</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="47" name="グループ化 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{004F3F62-47D1-BC51-DFF7-9F0ED8E46C28}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="351121" y="79434764"/>
-          <a:ext cx="10650071" cy="6593157"/>
-          <a:chOff x="339542" y="78544269"/>
-          <a:chExt cx="10804712" cy="6506498"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="45" name="図 44">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6873E121-8392-01C3-D83F-184CC249298C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="339542" y="78544269"/>
-            <a:ext cx="10804712" cy="6506498"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="35" name="正方形/長方形 34">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{828AF725-092D-453E-8BEC-56E0FCC4DAA2}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="388381" y="79330593"/>
-            <a:ext cx="2881725" cy="5534810"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="36" name="正方形/長方形 35">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3028BAD8-A715-4F55-8093-7DB56E4F3C6B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5206253" y="84529361"/>
-            <a:ext cx="1159809" cy="326849"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>18143</xdr:colOff>
       <xdr:row>377</xdr:row>
@@ -3698,7 +2848,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3717,23 +2867,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>395</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>206188</xdr:colOff>
+      <xdr:row>394</xdr:row>
+      <xdr:rowOff>170329</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>419</xdr:row>
-      <xdr:rowOff>146829</xdr:rowOff>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>144556</xdr:colOff>
+      <xdr:row>420</xdr:row>
+      <xdr:rowOff>57182</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="43" name="グループ化 42">
+        <xdr:cNvPr id="62" name="グループ化 61">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1018CE93-D0B7-9744-07DE-D5E3E492AC37}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EADACE67-5064-85E5-FB79-43CF8E658ABC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3741,18 +2891,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="463176" y="91477353"/>
-          <a:ext cx="10650071" cy="5704947"/>
-          <a:chOff x="469900" y="89839800"/>
-          <a:chExt cx="10801350" cy="5633229"/>
+          <a:off x="206188" y="92004776"/>
+          <a:ext cx="10660156" cy="5946994"/>
+          <a:chOff x="206188" y="90238729"/>
+          <a:chExt cx="10804488" cy="5830453"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="40" name="図 39">
+          <xdr:cNvPr id="61" name="図 60">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3123DC1F-E3D1-3494-CBC2-CFAA496AF9BF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABDA762E-2AE7-7B4E-9204-9E5A7122D1FD}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3761,15 +2911,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="469900" y="89839800"/>
-            <a:ext cx="10801350" cy="4919484"/>
+            <a:off x="206188" y="90238729"/>
+            <a:ext cx="10804488" cy="5213524"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3789,8 +2939,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="984623" y="94869000"/>
-            <a:ext cx="2461560" cy="604029"/>
+            <a:off x="962540" y="95467065"/>
+            <a:ext cx="2473783" cy="602117"/>
           </a:xfrm>
           <a:prstGeom prst="wedgeRectCallout">
             <a:avLst>
@@ -3871,8 +3021,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1551641" y="91124741"/>
-            <a:ext cx="3162299" cy="1105647"/>
+            <a:off x="1453179" y="91655154"/>
+            <a:ext cx="3450515" cy="914400"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -3942,8 +3092,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="463176" y="99351354"/>
-          <a:ext cx="10650071" cy="4258545"/>
+          <a:off x="466165" y="99992330"/>
+          <a:ext cx="10717306" cy="4285440"/>
           <a:chOff x="469900" y="98069401"/>
           <a:chExt cx="10801350" cy="4204757"/>
         </a:xfrm>
@@ -3962,7 +3112,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4144,8 +3294,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="522941" y="105282999"/>
-          <a:ext cx="10650071" cy="6408786"/>
+          <a:off x="525930" y="105961328"/>
+          <a:ext cx="10718800" cy="6450622"/>
           <a:chOff x="529665" y="103926340"/>
           <a:chExt cx="10804712" cy="6325116"/>
         </a:xfrm>
@@ -4164,7 +3314,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4263,8 +3413,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="478117" y="57008059"/>
-          <a:ext cx="10650071" cy="4831928"/>
+          <a:off x="481106" y="57375612"/>
+          <a:ext cx="10718800" cy="4863304"/>
           <a:chOff x="484841" y="56272953"/>
           <a:chExt cx="10804712" cy="4769175"/>
         </a:xfrm>
@@ -4283,7 +3433,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4353,6 +3503,1101 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>224117</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>201708</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>221129</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>78806</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4" name="グループ化 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB622133-E0EE-F9BA-D5A9-E9E16D730577}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="457199" y="10923496"/>
+          <a:ext cx="10718801" cy="6636486"/>
+          <a:chOff x="460337" y="10717308"/>
+          <a:chExt cx="10863132" cy="6506498"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="24" name="グループ化 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE418A9D-CDFD-601C-149F-DBF4B8C80635}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="460337" y="10717308"/>
+            <a:ext cx="10863132" cy="6506498"/>
+            <a:chOff x="459067" y="10717308"/>
+            <a:chExt cx="10804712" cy="6506498"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="23" name="図 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED353DAB-A919-4F2C-8C52-F7409EE1E779}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="459067" y="10717308"/>
+              <a:ext cx="10804712" cy="6506498"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="正方形/長方形 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47E50CF8-B305-43FB-A6C6-101537862BFB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5193966" y="11201771"/>
+              <a:ext cx="3443925" cy="331650"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="正方形/長方形 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58089218-FD46-281A-D19C-7E7C6F409CB3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3520554" y="12136120"/>
+              <a:ext cx="5139425" cy="608713"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="8" name="正方形/長方形 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36D47D2D-C69E-E03F-2546-3AAA43961B5A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8777110" y="11815068"/>
+              <a:ext cx="2305309" cy="396753"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="2" name="図 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DF32AF8-7BAE-4E67-BE58-FCE8AFB8A18E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="481403" y="10744201"/>
+            <a:ext cx="250353" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>72339</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="13" name="グループ化 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB266242-0DE4-75A2-E97E-C28AD12D8FAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="466165" y="1165412"/>
+          <a:ext cx="10717306" cy="7997139"/>
+          <a:chOff x="472440" y="1143000"/>
+          <a:chExt cx="10858500" cy="7844739"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="図 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F476092-5A66-293C-C917-B3765571034D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="472440" y="1143000"/>
+            <a:ext cx="10858500" cy="7844739"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="9" name="図 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FACFC9C3-EDB2-4E1D-A950-FD5DB2234E98}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="508297" y="1178858"/>
+            <a:ext cx="250353" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>7472</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>116159</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="37" name="グループ化 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{409BAA00-ED9B-8F81-E546-253E290F6D79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="466165" y="18654060"/>
+          <a:ext cx="10717306" cy="6634993"/>
+          <a:chOff x="472440" y="18295472"/>
+          <a:chExt cx="10858500" cy="6509487"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="44" name="グループ化 43">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA74142D-2B48-E12C-8C57-0768AE39B595}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="472440" y="18295472"/>
+            <a:ext cx="10858500" cy="6509487"/>
+            <a:chOff x="469900" y="18310414"/>
+            <a:chExt cx="10801350" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="38" name="図 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C27DE72-12A1-671D-F9A9-A5A99D9431EF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="18310414"/>
+              <a:ext cx="10801350" cy="6509487"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="正方形/長方形 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C7D4346-2743-47D1-97EE-E86C211126A3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5217465" y="18782646"/>
+              <a:ext cx="3442756" cy="335950"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="正方形/長方形 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78B252B8-1B3C-4915-8925-69E22E8AB1BA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3547271" y="19720078"/>
+              <a:ext cx="5134729" cy="813751"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="正方形/長方形 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACD207F6-E661-4551-AE4E-735EDCA28E53}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8800851" y="19400875"/>
+              <a:ext cx="2306640" cy="722803"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="34" name="図 33">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4C6061E-C52D-41D6-A3F4-718292A23016}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="481405" y="18323858"/>
+            <a:ext cx="250353" cy="221455"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>272</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>307</xdr:row>
+      <xdr:rowOff>188258</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="56" name="グループ化 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34320FDB-248B-E498-AD6D-1EA52C6C64ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="466165" y="63398401"/>
+          <a:ext cx="8573844" cy="8346139"/>
+          <a:chOff x="472440" y="62179201"/>
+          <a:chExt cx="8686800" cy="8189257"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="30" name="グループ化 29">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4852424-7306-A2E5-AA62-C59425A66CBE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="472440" y="62179201"/>
+            <a:ext cx="8686800" cy="8189257"/>
+            <a:chOff x="469900" y="61722001"/>
+            <a:chExt cx="8641080" cy="8189257"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="26" name="図 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05AD6181-0912-2CE4-3FFA-EB8CA8896AEE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="469900" y="61722001"/>
+              <a:ext cx="8641080" cy="8189257"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="正方形/長方形 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{094D0CCA-FA1E-42B3-9802-5B8F43E9A4D0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="596901" y="65660494"/>
+              <a:ext cx="872564" cy="318247"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="29" name="正方形/長方形 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BBBC4DF-764A-DA27-9ABB-9C4862B96257}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="604371" y="62872470"/>
+              <a:ext cx="6056405" cy="318247"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="55" name="図 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C337BE0-5283-4BE9-AD05-43E2E4FC8A05}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="508297" y="62232989"/>
+            <a:ext cx="250353" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>119533</xdr:colOff>
+      <xdr:row>343</xdr:row>
+      <xdr:rowOff>2988</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>116545</xdr:colOff>
+      <xdr:row>371</xdr:row>
+      <xdr:rowOff>108686</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="60" name="グループ化 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E75DC51C-D9EF-2ACB-AB95-F98F1CF4DACB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="352615" y="79950235"/>
+          <a:ext cx="10718801" cy="6632004"/>
+          <a:chOff x="355753" y="78412788"/>
+          <a:chExt cx="10863132" cy="6506498"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="47" name="グループ化 46">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{004F3F62-47D1-BC51-DFF7-9F0ED8E46C28}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="355753" y="78412788"/>
+            <a:ext cx="10863132" cy="6506498"/>
+            <a:chOff x="339542" y="78544269"/>
+            <a:chExt cx="10804712" cy="6506498"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="45" name="図 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6873E121-8392-01C3-D83F-184CC249298C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="339542" y="78544269"/>
+              <a:ext cx="10804712" cy="6506498"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="35" name="正方形/長方形 34">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{828AF725-092D-453E-8BEC-56E0FCC4DAA2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="388381" y="79330593"/>
+              <a:ext cx="2881725" cy="5534810"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="36" name="正方形/長方形 35">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3028BAD8-A715-4F55-8093-7DB56E4F3C6B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5206253" y="84529361"/>
+              <a:ext cx="1159809" cy="326849"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="59" name="図 58">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A2E5B46-1449-49D2-A837-2D77745826E3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="379656" y="78436695"/>
+            <a:ext cx="250352" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -5369,12 +5614,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758C1087-7522-4DC4-A1A0-48CB557D7600}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A2:B602"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5382,26 +5627,26 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B33" s="2"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B39" s="2"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B41" s="4"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>0</v>
       </c>
@@ -5409,39 +5654,39 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B43" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B44" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B45" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B46" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B50" s="2"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B72" s="2"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B74" s="5"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B75" s="5"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
         <v>0</v>
       </c>
@@ -5449,29 +5694,29 @@
         <v>56</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B78" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B79" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B90" s="2"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B100" s="2"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B103" s="2"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B105" s="6"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
         <v>0</v>
       </c>
@@ -5479,47 +5724,47 @@
         <v>63</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B112" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B113" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B114" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B115" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B116" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B118" s="2"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B133" s="2"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B137" s="2"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B139" s="7"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B147" s="2"/>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
         <v>0</v>
       </c>
@@ -5527,26 +5772,26 @@
         <v>67</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B150" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B151" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B167" s="2"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B169" s="4"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B171" s="2"/>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
         <v>0</v>
       </c>
@@ -5554,26 +5799,26 @@
         <v>69</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B185" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B186" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B187" s="2"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B198" s="2"/>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B214" s="2"/>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A218" s="1" t="s">
         <v>0</v>
       </c>
@@ -5581,23 +5826,23 @@
         <v>73</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B219" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B220" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B234" s="2"/>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B242" s="2"/>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A243" s="1" t="s">
         <v>0</v>
       </c>
@@ -5605,28 +5850,28 @@
         <v>76</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B244" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B245" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B246" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B250" s="2"/>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B263" s="2"/>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A269" s="1" t="s">
         <v>0</v>
       </c>
@@ -5634,29 +5879,29 @@
         <v>80</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B270" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B271" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B274" s="2"/>
     </row>
-    <row r="278" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B278" s="2"/>
     </row>
-    <row r="297" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B297" s="2"/>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B309" s="2"/>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A310" s="1" t="s">
         <v>0</v>
       </c>
@@ -5664,23 +5909,23 @@
         <v>83</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B311" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B312" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B314" s="2"/>
     </row>
-    <row r="321" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="321" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B321" s="2"/>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A339" s="1" t="s">
         <v>0</v>
       </c>
@@ -5688,31 +5933,31 @@
         <v>86</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B340" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B341" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B342" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B350" s="2"/>
     </row>
-    <row r="353" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B353" s="3"/>
     </row>
-    <row r="356" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B356" s="2"/>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A374" s="1" t="s">
         <v>0</v>
       </c>
@@ -5720,28 +5965,28 @@
         <v>90</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B375" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B376" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B377" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B383" s="2"/>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B387" s="2"/>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A392" s="1" t="s">
         <v>0</v>
       </c>
@@ -5749,23 +5994,23 @@
         <v>104</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B393" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B394" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="412" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="412" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B412" s="2"/>
     </row>
-    <row r="413" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="413" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B413" s="2"/>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A422" s="1" t="s">
         <v>0</v>
       </c>
@@ -5773,43 +6018,43 @@
         <v>105</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B423" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B424" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B425" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B426" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B427" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B428" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="439" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="439" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B439" s="2"/>
     </row>
-    <row r="448" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="448" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B448" s="2"/>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
         <v>0</v>
       </c>
@@ -5817,39 +6062,39 @@
         <v>106</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B451" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B452" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B453" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B454" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="465" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="465" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B465" s="2"/>
     </row>
-    <row r="498" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="498" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B498" s="2"/>
     </row>
-    <row r="540" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="540" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B540" s="2"/>
     </row>
-    <row r="567" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="567" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B567" s="2"/>
     </row>
-    <row r="602" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="602" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B602" s="2"/>
     </row>
   </sheetData>
@@ -5864,12 +6109,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16622AB1-2853-4282-ACE0-64F3E064F651}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:B589"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5877,30 +6122,30 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B31" s="2"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -5908,28 +6153,28 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B39" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B40" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B47" s="2"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
         <v>0</v>
       </c>
@@ -5937,28 +6182,28 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B70" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B71" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B87" s="2"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B97" s="2"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
         <v>0</v>
       </c>
@@ -5966,26 +6211,26 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B101" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B102" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B111" s="2"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B115" s="2"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B130" s="2"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
         <v>0</v>
       </c>
@@ -5993,20 +6238,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B135" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B136" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B144" s="2"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
         <v>0</v>
       </c>
@@ -6014,23 +6259,23 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B165" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B166" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B168" s="2"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B183" s="2"/>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
         <v>0</v>
       </c>
@@ -6038,33 +6283,33 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B195" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B196" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B197" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B198" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B210" s="2"/>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B229" s="2"/>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A237" s="1" t="s">
         <v>0</v>
       </c>
@@ -6072,26 +6317,26 @@
         <v>26</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B238" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B239" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B245" s="2"/>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B258" s="2"/>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B267" s="2"/>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A271" s="1" t="s">
         <v>0</v>
       </c>
@@ -6099,38 +6344,38 @@
         <v>29</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B272" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B273" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B274" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B275" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="276" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B276" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="290" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B290" s="2"/>
     </row>
-    <row r="302" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="302" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B302" s="2"/>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A305" s="1" t="s">
         <v>0</v>
       </c>
@@ -6138,31 +6383,31 @@
         <v>34</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B306" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B307" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B308" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B312" s="2"/>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B341" s="2"/>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B344" s="3"/>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A347" s="1" t="s">
         <v>0</v>
       </c>
@@ -6170,25 +6415,25 @@
         <v>40</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B348" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B349" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B350" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B372" s="2"/>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A376" s="1" t="s">
         <v>0</v>
       </c>
@@ -6196,54 +6441,54 @@
         <v>44</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B377" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B378" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B379" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B380" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B381" s="2"/>
     </row>
-    <row r="399" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="399" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B399" s="2"/>
     </row>
-    <row r="400" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="400" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B400" s="2"/>
     </row>
-    <row r="426" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="426" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B426" s="2"/>
     </row>
-    <row r="435" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="435" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B435" s="2"/>
     </row>
-    <row r="452" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="452" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B452" s="2"/>
     </row>
-    <row r="485" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="485" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B485" s="2"/>
     </row>
-    <row r="527" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="527" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B527" s="2"/>
     </row>
-    <row r="554" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="554" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B554" s="2"/>
     </row>
-    <row r="589" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="589" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B589" s="2"/>
     </row>
   </sheetData>
